--- a/excel_first.xlsx
+++ b/excel_first.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d70301f1f55ee4a6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{8CACA07D-2AA5-4F8F-A81F-39380E512422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40B8C71D-799A-4270-87D2-EB4DA467F3D5}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8CACA07D-2AA5-4F8F-A81F-39380E512422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36CC6F4-49A5-4400-947E-B90B159B8060}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{732B6B2B-9D62-46F4-BD51-2A50D454E9F3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="59">
   <si>
     <t>Monday</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>net saary</t>
+  </si>
+  <si>
+    <t>attendence</t>
+  </si>
+  <si>
+    <t>present</t>
+  </si>
+  <si>
+    <t>absent</t>
   </si>
 </sst>
 </file>
@@ -295,30 +304,182 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -631,735 +792,734 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="3"/>
-    <col min="2" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="4">
+      <c r="E1" s="3">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>4</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>7</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3">
         <v>8</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>9</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>10</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>11</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
         <v>11</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>12</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>12</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>13</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>14</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14">
         <v>14</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>15</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>15</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>0</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>16</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>16</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>17</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17">
         <v>17</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>18</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>19</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>20</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>21</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="2">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>23</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>24</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>25</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>26</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>27</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>28</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>29</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>30</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>31</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>32</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>33</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>34</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>35</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>36</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>37</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>7</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>38</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1375,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF81846-4DB7-4C85-9BCA-4D9ADE9E1CE3}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
@@ -1383,72 +1543,76 @@
     <col min="16" max="16" width="16.28515625" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="W1" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="3">
         <v>50000</v>
       </c>
       <c r="G2" t="s">
@@ -1471,6 +1635,7 @@
         <v>1</v>
       </c>
       <c r="L2">
+        <f>MAX(A2:A11)</f>
         <v>10</v>
       </c>
       <c r="M2" t="str">
@@ -1494,20 +1659,24 @@
         <v>1800</v>
       </c>
       <c r="T2">
+        <f>SUM(P2:Q2)-SUM(R2:S2)</f>
         <v>31200</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="W2" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="3">
         <v>30000</v>
       </c>
       <c r="G3" t="s">
@@ -1526,7 +1695,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <f>MIN(B2:B11)</f>
+        <v>4</v>
       </c>
       <c r="M3" t="str">
         <f>UPPER(B2:B11)</f>
@@ -1545,26 +1715,31 @@
         <v>1800</v>
       </c>
       <c r="T3">
+        <f>SUM(P3:Q3)-SUM(R3:S3)</f>
         <v>31200</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="W3" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="3">
         <v>40000</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
       <c r="H4">
+        <f>COUNT(C2:C11)</f>
         <v>0</v>
       </c>
       <c r="I4">
@@ -1576,6 +1751,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K4">
+        <f>MIN(C1:C11)</f>
         <v>0</v>
       </c>
       <c r="M4" t="s">
@@ -1594,20 +1770,24 @@
         <v>1800</v>
       </c>
       <c r="T4">
+        <f>SUM(P4:Q4)-SUM(R4:S4)</f>
         <v>56200</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="W4" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="3">
         <v>40000</v>
       </c>
       <c r="G5" t="s">
@@ -1626,118 +1806,189 @@
         <v>39000</v>
       </c>
       <c r="K5">
+        <f>MIN(D2:D11)</f>
         <v>30000</v>
       </c>
       <c r="L5">
+        <f>MAX(D2:D11)</f>
         <v>50000</v>
       </c>
       <c r="M5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="W5" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="3">
         <v>30000</v>
       </c>
       <c r="M6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="W6" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="3">
         <v>50000</v>
       </c>
       <c r="M7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="W7" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="3">
         <v>30000</v>
       </c>
       <c r="M8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="W8" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="3">
         <v>40000</v>
       </c>
       <c r="M9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="W9" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="3">
         <v>40000</v>
       </c>
       <c r="M10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="W10" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="3">
         <v>40000</v>
       </c>
       <c r="M11" t="s">
         <v>49</v>
       </c>
+      <c r="W11" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W12" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W13" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W14" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W15" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W16" s="8" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="T4">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThan">
+      <formula>50000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="lessThan">
+      <formula>35000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T3">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+      <formula>35000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W16">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"present"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"absent"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>